--- a/static/exports/students.xlsx
+++ b/static/exports/students.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>history_marks</t>
+          <t>social_science_marks</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -486,7 +486,37 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>second_language_marks</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>profile_pic</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>session_token</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>exam_fee_paid</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>exam_fee_payment_time</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>last_login</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>last_login_ip</t>
         </is>
       </c>
     </row>
@@ -536,9 +566,31 @@
       <c r="K2" t="n">
         <v>80</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="n">
+        <v>88</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>WhatsApp_Image_2024-11-28_at_17.03.18_7f1816d2.jpg</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-05-16 13:35:01</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2025-05-21 20:15:11</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
         </is>
       </c>
     </row>
@@ -588,11 +640,21 @@
       <c r="K3" t="n">
         <v>90</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>98</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>demo-image2.png</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -640,11 +702,29 @@
       <c r="K4" t="n">
         <v>77</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>90</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>IMG_20250128_094323.jpg</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3abb5b10-b106-4733-81f8-fff7032af9cd</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-05-14 11:45:39</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -692,11 +772,29 @@
       <c r="K5" t="n">
         <v>96</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>95</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>IMG_20241010_184554002_HDR.jpg</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>24805b4b-5dad-48e5-85f7-3505c1b76f75</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-05-14 11:50:06</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -744,11 +842,21 @@
       <c r="K6" t="n">
         <v>80</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>69</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>IMG_8720.jpeg</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -796,11 +904,21 @@
       <c r="K7" t="n">
         <v>77</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>66</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>default.png</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -848,11 +966,21 @@
       <c r="K8" t="n">
         <v>70</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>87</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>IMG20250405123531.jpg</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -889,22 +1017,36 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J9" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="K9" t="n">
+        <v>74</v>
+      </c>
+      <c r="L9" t="n">
         <v>99</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>IMG-20250326-WA0013.jpg</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>c2f94b81f4196acf70f59d51f55f54c6be21cf913b8cbf0e</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -952,11 +1094,29 @@
       <c r="K10" t="n">
         <v>54</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>20250510_203843.jpg</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6366ee81-1b2d-4d52-92e0-1dfe91c453ac</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-05-14 11:37:16</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
